--- a/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Johnston Paper/Johnston Paper_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Napkin White - Not Interfolded</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
